--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0017.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0017.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Haha, không có gì.</t>
+          <t>Haha, không có gì đâu.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Tôi có linh cảm cậu khác với những người không bao giờ trở lại.</t>
+          <t>Ta có linh cảm ngươi khác với những kẻ không bao giờ trở về.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dù bạn đi xa đến đâu, khi mệt mỏi, bạn luôn được chào đón trở về Núi Firmament.</t>
+          <t>Dù đi xa đến đâu, khi mệt mỏi, cậu luôn được chào đón trở về Núi Firmament.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Cậu biết nơi tìm tớ mà. Hãy báo cho tớ khi nào muốn hàn huyên bên ấm trà nhé.</t>
+          <t>Cậu biết tìm ta ở đâu. Khi nào muốn hàn huyên bên ấm trà, cứ báo ta nhé.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>(Một cuộc gọi từ số lạ... Chuyện gì vậy?)</t>
+          <t>(Một cuộc gọi từ số lạ... Chẳng biết có chuyện gì?)</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Này, là {PlayerName} phải không? Tôi hy vọng cuối cùng cũng liên lạc được đúng người...</t>
+          <t>Này, có phải {PlayerName} không? Hy vọng lần này tao gọi đúng người rồi...</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vâng, tôi đang nghe. Còn cậu là?</t>
+          <t>Vâng, tôi đang nghe. Còn cậu là ai?</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tôi không quan tâm đến sản phẩm của bạn, cảm ơn.</t>
+          <t>Cảm ơn, nhưng tôi không quan tâm đến sản phẩm của anh đâu.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Hello, tôi là Vida, đang kinh doanh nhỏ ở Thị trấn Egla.</t>
+          <t>Chào cậu, mình là Vida, đang kinh doanh nhỏ ở thị trấn Egla.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ồ, đừng lo. Tôi không gọi điện lạnh đâu. Tôi chỉ kinh doanh nhỏ ở Thị trấn Egla thôi. Cứ gọi tôi là Vida.</t>
+          <t>Ồ, đừng lo. Tôi không đi chào hàng đâu. Tôi chỉ làm ăn nhỏ ở Thị trấn Egla thôi. Cứ gọi tôi là Vida nhé.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Tôi đã gặp bạn ở đâu rồi, phải không?</t>
+          <t>Ta gặp cậu rồi phải không?</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Tôi có thể giúp gì cho bạn?</t>
+          <t>Tôi có thể làm gì cho cậu?</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bạn đã từng thấy những bức tranh sặc sỡ này đứng giữa cánh đồng hoang tàn chưa?</t>
+          <t>Cậu có từng thấy những bức tranh sặc sỡ này đứng giữa cánh đồng hoang tàn ngoài kia không?</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Như thể thế giới xung quanh đã mất hết màu sắc?</t>
+          <t>Như thể thế giới xung quanh đã mất đi sắc màu?</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Như thể thế giới xung quanh đã mất đi sinh khí?</t>
+          <t>Như thể thế giới xung quanh đã mất đi sức sống?</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Những hiện tượng kỳ lạ như vậy đã âm thầm lan rộng khắp Rinascita, khiến người dân bình thường hoàn toàn bất lực…</t>
+          <t>Những hiện tượng kỳ lạ như thế này đã âm thầm lan rộng khắp Rinascita, khiến người dân bình thường hoàn toàn bất lực…</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Tôi vừa khôi phục được một vị trí.</t>
+          <t>Ta vừa khôi phục được một chỗ.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Chờ đã... anh làm được thật à? Tôi biết anh chính là người tôi cần gặp.</t>
+          <t>Chờ đã... cậu làm rồi à? Tớ biết cậu là người nên nói chuyện mà.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hãy ghé qua tìm tôi ở Thị trấn Egla khi rảnh nhé. Tôi có việc cần nhờ cậu, chúng ta sẽ bàn chi tiết khi gặp nhau.</t>
+          <t>Khi nào rảnh, hãy đến tìm tôi ở Egla Town nhé. Tôi có việc muốn nhờ cậu, chi tiết sẽ bàn sau khi gặp mặt.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>(Cuộc gọi đã kết thúc.)</t>
+          <t>Cuộc gọi đã kết thúc.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Hắt xì—Vừa thức dậy đã nghe mấy người nói chuyện rồi...</t>
+          <t>Hơ... Vừa tỉnh dậy đã nghe mấy người nói chuyện rồi...</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Khoan, người này có vẻ khả nghi. Sao cô ấy biết thông tin liên lạc của bạn?</t>
+          <t>Đợi đã, người này có gì đó khả nghi. Sao cô ta biết thông tin liên lạc của cậu?</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Bởi vì ta chính là Rover nổi tiếng!</t>
+          <t>Tao là Rover nổi tiếng đây!</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Cuối cùng thì cậu cũng đến! Tôi vừa tự hỏi còn phải đợi bao lâu nữa đây.</t>
+          <t>Cuối cùng cậu cũng đến! Tớ đang tự hỏi phải đợi thêm bao lâu nữa đây.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Bởi vì... "Hãy cùng hướng tới một thế giới của những khám phá và điều kỳ diệu."</t>
+          <t>Bởi vì... "Hãy cùng chào đón một thế giới đầy khám phá và kỳ diệu."</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Hừm, nghe quen quen. Đó không phải là khẩu hiệu của Pioneer Association sao?</t>
+          <t>Hừm, nghe quen quen. Chẳng phải khẩu hiệu của Hiệp hội Pioneer sao?</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Bạn có thuộc Hiệp hội Tiên phong không?</t>
+          <t>Cậu thuộc Hiệp hội Pioneer à?</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Nhưng sâu thẳm trong lòng, tôi vẫn không thể vượt qua những cảnh vật đã phai mờ.</t>
+          <t>Nhưng sâu thẳm trong lòng, ta vẫn không thể vượt qua những cảnh vật đã phai nhòa.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Bạn muốn tôi khôi phục những khu vực đó chứ?</t>
+          <t>Cậu muốn ta khôi phục những khu vực đó không?</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Nếu giờ đây ta chỉ còn nhìn thấy những cảnh vật quen thuộc qua những bức ảnh... thật là một suy nghĩ đáng buồn, phải không?</t>
+          <t>Nếu từ giờ chỉ còn nhìn thấy những cảnh vật quen thuộc qua ảnh... thật là một suy nghĩ u ám, phải không?</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Hãy bàn bạc điều khoản trước đã.</t>
+          <t>Trước hết, bàn về điều khoản đã.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hay là thêm chút gì đó để thỏa thuận thêm hấp dẫn nhé?</t>
+          <t>Hay là thêm một chút "gia vị" cho thỏa thuận này nhỉ?</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Khôi phục các khu vực không chỉ mang lại màu sắc mà còn cả tài nguyên. Cậu có thể đổi chúng với tôi để lấy một số... vật phẩm hiếm trên thị trường.</t>
+          <t>Khôi phục các khu vực không chỉ mang lại màu sắc mà còn cả tài nguyên. Ngươi có thể đổi chúng với ta để lấy... những món đồ hiếm trên thị trường.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Nghe có vẻ đây mới là ý định thực sự của cô ấy...</t>
+          <t>Nghe như đây mới là mục đích thật sự của cô ta...</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Là một thương nhân, đây là kỹ năng cơ bản của tôi. Vậy bạn thấy sao? Những mặt hàng và ưu đãi này chỉ dành riêng cho đối tác thôi.</t>
+          <t>Là một thương nhân, đây là kỹ năng cơ bản của tôi. Thế nào, ưng ý không? Những món hàng và ưu đãi này chỉ dành riêng cho đối tác thôi.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Hiểu rồi, hãy chốt thỏa thuận nào.</t>
+          <t>Đã rõ, bắt đầu thôi.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Được rồi, xem thử hàng trên kệ đi. Những tài nguyên này chính là thứ cậu cần ngay lúc này.</t>
+          <t>Được rồi, xem thử những gì trên kệ đi. Những tài nguyên này là thứ cậu đang cần đấy.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Cảm ơn quý khách đã ủng hộ. Từ giờ chúng ta là đối tác lâu dài rồi.</t>
+          <t>Cảm ơn vì đã ủng hộ. Từ giờ trở đi, chúng ta là đối tác lâu dài.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Hãy cùng nhau giành lại màu sắc tự nhiên cho thế giới của chúng ta!</t>
+          <t>Hãy cùng nhau giành lại sắc màu tự nhiên cho thế giới này!</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>À phải, còn gì khác cậu muốn hỏi không? Với một đối tác quan trọng như cậu, mình luôn sẵn sàng chia sẻ tất cả.</t>
+          <t>À phải, còn gì muốn hỏi nữa không? Với một đối tác quan trọng như cậu, tao luôn sẵn sàng chia sẻ hết.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Những vật phẩm hiếm này từ đâu ra vậy?</t>
+          <t>Những món đồ hiếm này từ đâu mà có?</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Sao không mở rộng kinh doanh ở Thành phố Ragunna nhỉ?</t>
+          <t>Sao không mở rộng kinh doanh ở Thành phố Ragunna?</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bạn có bao giờ nhớ cuộc sống du hành của mình không?</t>
+          <t>Cậu có bao giờ nhớ cuộc sống du hành không?</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Trong những chuyến du hành khắp Rinascita, tớ đã xây dựng một mạng lưới đối tác kinh doanh, nhiều người trong số họ cung cấp cho tớ những nguồn hàng độc đáo.</t>
+          <t>Trong những chuyến đi qua Rinascita, ta đã xây dựng được mạng lưới đối tác kinh doanh, nhiều người trong số họ cung cấp cho ta những nguồn hàng độc đáo.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Chẳng phải đây là... hàng lậu sao?</t>
+          <t>Vậy đây chẳng phải là... hàng lậu sao?</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Thư giãn đi. Chẳng ai đến gõ cửa nhà bạn đâu. Và dù có đến... chắc bạn cũng xử lý được, phải không?</t>
+          <t>Thư giãn đi. Chẳng ai đến gõ cửa nhà cậu đâu. Dù có đến... chắc cậu cũng xử lý được, phải không?</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Thị trấn Egla là quê hương của tôi. Mỗi khi đứng trên cao ngắm những chiếc cối xay gió quay trong gió, tôi lại cảm thấy bình yên.</t>
+          <t>Thị Trấn Egla là quê hương của tớ. Mỗi khi đứng trên cao ngắm những chiếc cối xay gió quay trong gió, tớ lại cảm thấy bình yên đến lạ.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tôi không chắc mình hiểu đúng.</t>
+          <t>Tôi không chắc mình hiểu đúng không.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Anyway... Mặc dù mình sống ở thị trấn, nhưng mình thực ra có giao dịch với một số cửa hàng trong thành phố. Có thể cậu đã gián tiếp mua hàng của mình rồi đấy.</t>
+          <t>Dù sao... Dù tớ sống ở thị trấn này, nhưng tớ vẫn có giao dịch với vài cửa hàng trong thành phố. Có thể cậu đã vô tình mua hàng của tớ rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Tất nhiên, tôi thường xem lại những bức ảnh chụp trong chuyến đi, hồi tưởng lại những khoảnh khắc vui vẻ và thử thách trên đường.</t>
+          <t>Tất nhiên, ta thường xem lại những bức ảnh chụp trong chuyến đi, hồi tưởng lại những khoảnh khắc vui vẻ và thử thách trên đường.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Một số mặt hàng trên kệ có số lượng giới hạn, nhưng sẽ được bổ sung định kỳ. Hãy thường xuyên kiểm tra lại nhé!</t>
+          <t>Một số món đồ trên kệ có số lượng giới hạn, nhưng sẽ được bổ sung định kỳ. Nhớ ghé kiểm tra thường xuyên nhé!</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng cô ấy cư xử khác lạ phải không?</t>
+          <t>Thỉnh thoảng, cách hành xử của cô ấy lại thay đổi, phải không?</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Tôi nghe các bậc trưởng lão trong thị trấn kể rằng ở cuối Thiên Phàm Cốc có một hòn đảo huyền bí, xung quanh là khu rừng hình vòng tròn bao bọc một hồ nước trong như gương.</t>
+          <t>Ta nghe các trưởng lão trong thị trấn kể rằng ở cuối Whisperwind Haven có một hòn đảo huyền bí, bao quanh bởi khu rừng hình vòng cung ôm lấy hồ nước trong như gương.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hồ nước tĩnh lặng như gương, được cho là có thể phản chiếu "bản ngã sâu thẳm" bên trong mỗi người.</t>
+          <t>Hồ nước tĩnh lặng như gương, được cho là có thể phản chiếu "bản ngã sâu thẳm" của mỗi người.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Dường như... chưa ai thực sự đến được nơi đó.</t>
+          <t>Có vẻ... chưa ai thực sự đặt chân đến đó cả.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Còn bạn là...?</t>
+          <t>Và ngươi là?</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Bạn có phải con mèo trắng lúc trước không?</t>
+          <t>Cậu là con mèo trắng lúc nãy à?</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Thôi nào, tôi biết bạn có thể nói chuyện mà.</t>
+          <t>Nào, tôi biết cậu nói được mà.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Dreamwalker, ngươi đã trở lại.</t>
+          <t>Dreamwalker, cậu đã trở lại rồi.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Rất vui được gặp bạn.</t>
+          <t>Rất vui được gặp cậu.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Người gác cổng Ebony không nhận ra tôi.</t>
+          <t>Ebony Gatekeeper không nhận ra tôi.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chẳng phải chúng ta vừa có một chuyến phiêu lưu hoành tráng sao? Tớ biết là cậu vẫn chưa thể hiểu hết mọi chuyện, phải không?</t>
+          <t>Chẳng phải tụi mình vừa có một chuyến phiêu lưu hoành tráng cùng nhau sao? Tao biết, cậu vẫn chưa thể hiểu nổi đâu, phải không?</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ừ, cậu thấy đấy… anh ấy đang gặp chút rắc rối.</t>
+          <t>Đúng thế... cậu thấy đấy, anh ấy đang gặp chút rắc rối.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Người đàn ông chào bạn ở cổng vào không phải là Ebony Gatekeeper thật sự.</t>
+          <t>Gã chào cậu ở cổng kia không phải là Người Gác Cổng Ebony thật đâu.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Không phải Gatekeeper Huyền Ngân thật sao?</t>
+          <t>Không phải Người Gác Cổng Ebony thật à?</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Sau trận chiến của cậu ở Somnoire, hắn đã tạm thời mất quyền kiểm soát cõi đó. Để bù đắp cho sự vắng mặt ngoài dự kiến của hắn, Somnoire đã kích hoạt bản sao dự phòng.</t>
+          <t>Sau trận chiến của cậu ở Somnoire, hắn tạm thời mất quyền kiểm soát vùng đất ấy. Để lấp đầy khoảng trống bất ngờ đó, Somnoire đã kích hoạt bản sao dự phòng của hắn.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Bản sao lưu chỉ giữ lại những ký ức hạn chế từ một thời điểm nhất định trong quá khứ, nên việc cậu ấy không nhớ chuyện đã xảy ra là điều dễ hiểu.</t>
+          <t>Bản sao lưu chỉ giữ lại những ký ức hạn chế từ một thời điểm nhất định trong quá khứ, nên cậu ấy không nhớ chuyện đã xảy ra cũng phải thôi.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Anh ấy nhờ tôi giúp khôi phục Somnoire.</t>
+          <t>Cậu ấy nhờ tôi giúp khôi phục Somnoire.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Vậy... lại có vấn đề gì nữa à?</t>
+          <t>Vậy... lại có rắc rối gì nữa à?</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Hiện tại, gã đó chỉ là dự bị thôi, nên có lẽ hắn chỉ đang làm nhiệm vụ của mình, đơn giản vậy thôi.</t>
+          <t>Hiện giờ, gã đó chỉ là dự bị thôi, nên chắc cũng chỉ làm nhiệm vụ cho có lệ.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Phía sau cánh cổng này ẩn chứa vô vàn bí ẩn. Sự hỗn loạn ở Somnoire vẫn chưa được giải quyết hoàn toàn, và tôi vẫn đang tiếp tục điều tra.</t>
+          <t>Phía sau cánh cổng này ẩn chứa đủ mọi bí ẩn. Sự hỗn loạn ở Somnoire vẫn chưa được giải quyết hoàn toàn, và ta vẫn đang tiếp tục điều tra.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Tôi sẽ ở đây để hỗ trợ bạn trên hành trình, như tôi đã từng làm trước đây.</t>
+          <t>Ta sẽ ở bên hỗ trợ cậu trên đường đi, như ta đã từng làm trước đây.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Tôi hy vọng điều này sẽ tạo nên sự khác biệt.</t>
+          <t>Hy vọng nó sẽ tạo nên sự khác biệt.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Tôi nên làm gì tiếp theo?</t>
+          <t>Giờ mình nên làm gì đây?</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Bạn có thể làm theo chỉ dẫn của "anh ấy" và tiếp tục khám phá.</t>
+          <t>Cậu cứ theo sự hướng dẫn của "hắn" mà tiếp tục khám phá đi.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Ý cậu là hoàn thành hướng dẫn cho người mới này à?</t>
+          <t>Ý cậu là hoàn thành hướng dẫn dành cho người mới này à?</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Cảm ơn, điều này sẽ giúp khôi phục một phần Vùng Ký Ức.</t>
+          <t>Cảm ơn cậu, điều này sẽ giúp khôi phục một phần Khu Vực Ký Ức.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Chính xác. "Hắn" đã nhầm cậu là người mới đến Somnoire và đã chuẩn bị một lộ trình đặc biệt cho cậu.</t>
+          <t>Chính xác. "Hắn" đã nhầm cậu là kẻ mới đến Somnoire và bày sẵn một lộ trình đặc biệt cho cậu đấy.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Nhưng sức mạnh thực sự của Gatekeeper Huyền Ngọc đang dần được khôi phục. Chẳng bao lâu nữa, bản sao dự phòng của hắn có thể sẽ bị loại bỏ...</t>
+          <t>Nhưng sức mạnh của Người Gác Cổng Hắc Ám thật sự đang dần hồi phục. Chẳng bao lâu nữa, bản sao dự phòng của hắn có thể sẽ bị vô hiệu hóa...</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Nhưng đó là chuyện của ngày khác. Hiện tại, con đường của bạn đã được định sẵn.</t>
+          <t>Nhưng đó là chuyện của ngày khác. Hiện tại, con đường của cậu đã được định sẵn rồi.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Sao lâu vậy mới rời khỏi Memory Zone đó?</t>
+          <t>Sao cậu lại mất nhiều thời gian thế để rời khỏi Vùng Ký Ức?</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Thôi, bỏ qua đi...</t>
+          <t>Thôi, bỏ đi...</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Ui, kẻ địch ở khắp nơi.</t>
+          <t>Ôi, kẻ địch ở khắp nơi.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Nhưng cậu xử lý chúng như thể là bản năng thứ hai vậy... Thật sự rất ấn tượng.</t>
+          <t>Nhưng cậu xử lý chúng như thể đó là bản năng thứ hai... Thật đáng nể.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Như bạn thấy đấy, chúng ta đang ở bên trong Somnoire. Bạn thấy thế nào?</t>
+          <t>Như anh thấy đấy, giờ chúng ta đang ở bên trong Somnoire. Anh thấy thế nào?</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Nó thật đẹp.</t>
+          <t>Thật đẹp.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Nó quen thuộc quá.</t>
+          <t>Quen thuộc thật.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Xét cho cùng, nó được tạo nên từ ký ức và ước mơ của vô số cá nhân.</t>
+          <t>Dù sao, nó cũng được tạo nên từ ký ức và giấc mơ của vô số người.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Giấc mơ thường đưa ta vượt xa những gì ta có thể tưởng tượng.</t>
+          <t>Giấc mơ thường đưa ta vượt xa khỏi những gì ta có thể tưởng tượng.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Quay lại vấn đề chính, trong Somnoire, cậu sẽ gặp những thực thể khác ngoài tôi.</t>
+          <t>Quay lại vấn đề chính, trong Somnoire, cậu sẽ gặp những thực thể khác ngoài tao.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Cô ấy…</t>
+          <t>Cô ấy là...</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Cô ấy là một thực thể ảo, sự kết hợp của vô số ý thức bên trong Somnoire, và là người đang trải nghiệm giấc mơ này.</t>
+          <t>Cô ấy là một thực thể ảo, sự kết hợp của vô số ý thức trong Somnoire, và cũng là người đang trải nghiệm giấc mơ này.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Hãy cứ coi cô ấy như một người đang mơ, nhưng thực ra cô ấy không hề tồn tại. Cô ấy chỉ là một Illusia được tạo ra bởi cánh cổng dẫn đến Somnoire.</t>
+          <t>Cứ coi cô ấy như một người đang mơ thôi, nhưng thực ra cô ấy không hề tồn tại. Cô ấy chỉ là một Illusia được tạo ra bởi cánh cổng dẫn đến Somnoire.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Tại sao cô ấy lại ở đây?</t>
+          <t>Sao cô ấy lại ở đây?</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Bởi vì phải có ai đó mơ thì giấc mơ mới tồn tại, phải không?</t>
+          <t>Bởi phải có ai đó mơ về giấc mơ thì giấc mơ mới tồn tại, phải không?</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Thực tế, cô ấy sẽ là đồng minh đắc lực khi bạn khám phá Somnoire.</t>
+          <t>Thực tế, cô ấy sẽ là đồng minh đắc lực khi cậu khám phá Somnoire đấy.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bạn không thể mang bất cứ thứ gì vào đây. Nếu cần gì trong trận chiến, bạn sẽ phải triệu hồi chúng từ những giấc mơ được ghi lại trong Somnoire.</t>
+          <t>Bạn không thể mang bất cứ thứ gì vào đây. Nếu cần gì trong trận chiến, anh sẽ phải triệu hồi chúng từ những giấc mơ được ghi lại trong Somnoire.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Chẳng hạn như... các Echoes bạn dùng trong trận chiến.</t>
+          <t>Như... những Echo cậu dùng trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Hãy đi nói chuyện với cô ấy. Cô ấy sẽ đưa cho cậu vài thứ quan trọng cho giấc mơ của cậu.</t>
+          <t>Đến nói chuyện với cô ấy đi. Cô ấy sẽ đưa cho cậu vài thứ quan trọng cho giấc mơ của cậu.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>À, xin chào. Cậu cũng đang mơ à?</t>
+          <t>À, chào cậu. Cậu cũng đang mơ à?</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bạn thực sự đang mơ à?</t>
+          <t>Cậu thực sự đang mơ đấy à?</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Đúng vậy, xin chào, người đồng mộng.</t>
+          <t>Ừ, xin chào, người mộng mơ đồng hành của ta.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Xin chào, cho mình xin một hai Echo đi.</t>
+          <t>Chào cậu, cho tớ xin một hai cái Echo được không?</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Đúng vậy, tôi đã mơ mãi mãi. Bạn sẽ không tin những điều tôi đã mơ đâu.</t>
+          <t>Ừ, tôi đã mơ mãi không thôi. Những điều tôi mơ, cậu không thể tin được đâu.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Haha, xin chào cậu! Chưa bao giờ thấy ai tràn đầy sức sống như cậu ở đây cả.</t>
+          <t>Haha, chào cậu! Tao chưa thấy ai ở đây sôi nổi như cậu bao giờ.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Không cần phải vội…</t>
+          <t>Không cần phải vội vàng đâu…</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Giờ cậu đã tìm thấy tớ, chắc là cậu muốn nghe về những giấc mơ của tớ nhỉ? Tớ đã mơ ra bao nhiêu điều tuyệt vời đấy!</t>
+          <t>Giờ cậu đã tìm đến tớ, chắc là muốn nghe về những giấc mơ của tớ hả? Tớ đã mơ thấy những điều tuyệt vời lắm đấy!</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Vừa nãy, tôi mơ thấy...</t>
+          <t>Vừa nãy, tớ mơ thấy...</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Vậy, cậu thấy thế nào? Những giấc mơ của tớ có thú vị không?</t>
+          <t>Vậy thì cậu thấy thế nào? Giấc mơ của tớ có thú vị không?</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Trong giấc mơ của bạn có một số thứ rất mạnh mẽ.</t>
+          <t>Trong giấc mơ của cậu có những thứ rất mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Cảm ơn vì đã chia sẻ ước mơ với tôi.</t>
+          <t>Cảm ơn anh đã chia sẻ những giấc mơ của mình với tôi.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hehe, ta có nói dối các cháu đâu, phải không?</t>
+          <t>Hehe, ta có nói dối cậu đâu, phải không?</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Không có gì! Tôi rất vui khi được chia sẻ điều đó với bạn.</t>
+          <t>Không có gì! Tớ rất vui vì đã được chia sẻ điều đó với cậu.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Tớ đã có bao nhiêu giấc mơ tuyệt vời, nhưng buồn thay, chẳng có ai ở đây để lắng nghe cả...</t>
+          <t>Ta đã có biết bao giấc mơ kỳ diệu... nhưng tiếc là chẳng có ai ở đây để nghe cả.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Tớ rất vui được chia sẻ ước mơ với cậu bất cứ lúc nào!</t>
+          <t>Tớ rất vui được chia sẻ giấc mơ của mình với cậu bất cứ lúc nào!</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Tại sao không phải bây giờ?</t>
+          <t>Sao không phải là bây giờ?</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Vì tôi biết cậu đến đây vì việc làm ăn, chứ không phải vì ước mơ của tôi.</t>
+          <t>Bởi vì ta hiểu cậu đến đây vì việc riêng, chứ không phải vì giấc mơ của ta.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Cậu biết là có gì đó không ổn ở đây, phải không?</t>
+          <t>Cậu biết có gì đó không ổn ở đây rồi, phải không?</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Gần đây có nhiều điều kỳ lạ đang tụ tập trong Somnoire, và tôi cũng thường gặp ác mộng...</t>
+          <t>Gần đây, những điều kỳ lạ cứ ùn ùn kéo về Somnoire, và tao cũng bắt đầu gặp ác mộng...</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Vậy nên tôi sẽ không giữ cậu lâu hơn. Nếu cậu có thể giúp khôi phục mọi thứ về bình thường, chúng ta sẽ có vô vàn thời gian để trò chuyện.</t>
+          <t>Vậy nên tớ sẽ không làm phiền cậu lâu đâu. Nếu cậu có thể giúp khôi phục mọi thứ về bình thường, chúng ta sẽ có cả đời để trò chuyện.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Thật tuyệt vời. Tôi cứ nghĩ…</t>
+          <t>Thật tuyệt vời. Tớ cứ tưởng…</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Bạn nghĩ gì?</t>
+          <t>Mày nghĩ gì cơ?</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Bạn nghĩ tôi sẽ bị đánh bại à?</t>
+          <t>Mày nghĩ ta sẽ bại trận à?</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tớ đã nghĩ nhiệm vụ này sẽ không dễ dàng, kể cả với một người như cậu.</t>
+          <t>Tôi đã nghĩ nhiệm vụ này sẽ không dễ dàng, ngay cả với một người như cậu.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Tôi đã đánh giá thấp bạn.</t>
+          <t>Ta đã đánh giá thấp ngươi.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Somnoire ngày càng hỗn loạn và nguy hiểm.</t>
+          <t>Somnoire ngày càng trở nên hỗn loạn và nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Gần đây, nó đang ngấu nghiến và sao chép mọi giấc mơ mà không phân biệt...</t>
+          <t>Gần đây, nó đang nuốt chửng và sao chép mọi giấc mơ mà không phân biệt...</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Bạn sẽ gặp phải nhiều hiện tượng kỳ lạ hơn ở Somnoire… Những sinh vật, thực vật, Tacet Discord, và thậm chí cả những người bạn thân thiết của bạn.</t>
+          <t>Con sẽ gặp nhiều điều kỳ lạ hơn ở Somnoire… Những sinh vật, thực vật, Tacet Discord, và thậm chí cả những người bạn thân thiết của con.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Dù bạn biết đây chỉ là giấc mơ, những cảnh tượng này vẫn có thể để lại tác động sâu sắc đến tâm trí bạn. Hy vọng bạn đã chuẩn bị sẵn sàng.</t>
+          <t>Dù biết đó chỉ là giấc mơ, nhưng những cảnh tượng này vẫn có thể để lại dấu ấn sâu đậm trong tâm trí cậu. Tôi hy vọng cậu đã chuẩn bị sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Dù sao… Hôm nay cậu làm tốt lắm. Tôi sẽ gặp cậu bên ngoài Cổng.</t>
+          <t>Dù sao… hôm nay cậu làm tốt lắm. Ta sẽ gặp cậu bên ngoài Cổng nhé.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Chúng không nên xuất hiện ở đây. Khu Vực Ký Ức này chắc hẳn đã bị hỏng.</t>
+          <t>Chúng không nên xuất hiện ở đây. Khu Vực Ký Ức này chắc đã bị nhiễm độc rồi.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Đừng coi thường chúng, Rover. Hãy cẩn thận. Chúng ta không biết loại kẻ địch nào có thể xuất hiện ở Somnoire hiện tại.</t>
+          <t>Đừng coi thường chúng, Rover à. Cẩn thận đấy. Ta chẳng biết loại kẻ thù nào có thể xuất hiện trong Somnoire hiện tại đâu.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tôi không rõ thứ đó là gì, nhưng Metaphor mà nó cung cấp chắc sẽ hữu dụng.</t>
+          <t>Tôi không rõ thứ đó là gì, nhưng phép Ẩn Dụ mà nó cung cấp chắc chắn sẽ hữu dụng.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Trong cõi mộng và ký ức này, không có thứ gọi là thực tại khách quan. Điều gì càng mơ hồ, càng chứa đựng nhiều khả năng.</t>
+          <t>Trong cõi mộng và ký ức này, không tồn tại thứ gọi là thực tại khách quan. Cái gì càng mù mờ, càng chứa đựng nhiều khả năng.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Chúng lại đến nữa rồi. Đám quái vật dai dẳng thật đấy.</t>
+          <t>Chúng lại kéo đến nữa rồi. Đám quái vật này thật dai dẳng.</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Ui, kẻ địch ở khắp nơi.</t>
+          <t>Ôi, kẻ địch ở khắp nơi.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Mình có thứ này cho cậu... Chắc chắn sẽ có ích vào lúc nào đó.</t>
+          <t>Tớ có thứ này cho cậu... Chắc chắn sẽ hữu dụng vào lúc nào đó thôi.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Anyway... Thấy cái vật kia không? Đó chính là thủ phạm gây ra sự hỗn loạn và hủ bại ở khu vực này...</t>
+          <t>Dù sao... Thấy cái thứ kia không? Chính nó là thủ phạm gây ra hỗn loạn và ô uế ở khu vực này...</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Nó trông khó đối phó đấy. Cậu nên tận dụng tốt các Echoes Ảo và Phép Ẩn Dụ mà mình có được cho đến nay.</t>
+          <t>Nó trông khó nhằn đấy. Cậu nên tận dụng tốt những Illusive Echoes và Metaphors mà mình có được cho đến giờ.</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Weapons tiêu chuẩn 5 sao có thể chọn</t>
+          <t>Vũ khí tiêu chuẩn 5 sao có thể chọn</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11625,8 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; x450 để chọn một trong các vũ khí sau: &lt;color=#ffd12f&gt;Laser Shearer, Radiance Cleaver, Phasic Homogenizer, Pulsation Bracer, Boson Astrolabe&lt;/color&gt;.</t>
+          <t>Tổng cộng đạt &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; x450
+để chọn một trong các vũ khí sau: &lt;color=#ffd12f&gt;Laser Shearer, Radiance Cleaver, Phasic Homogenizer, Pulsation Bracer, Boson Astrolabe&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13255,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng &lt;color=Highlight&gt;Stage 3 Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack Nâng Cao&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Cơ Bản&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Cơ Bản Nâng Cao&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Đồng Hồ Forte - Đỏ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13320,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng &lt;color=Highlight&gt;Stage 3 Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack Nâng Cao&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Cơ Bản&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Cơ Bản Nâng Cao&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Đồng Hồ Forte - Đỏ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13385,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng &lt;color=Highlight&gt;Stage 3 Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack Nâng Cao&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Cơ Bản&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Cơ Bản Nâng Cao&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Đồng Hồ Forte - Đỏ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13450,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Đồng Hồ Forte - Tím&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13514,7 +13515,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Đồng Hồ Forte - Tím&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13580,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt;.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Đồng Hồ Forte - Tím&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13645,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chuyển sang Rover.</t>
+          <t>Chuyển sang Rover đi</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13710,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Chuyển sang Rover.</t>
+          <t>Chuyển sang Rover đi</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13775,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Chuyển sang Rover.</t>
+          <t>Chuyển sang Rover đi</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13840,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Chuyển sang Phrolova.</t>
+          <t>Chuyển sang Phrolova đi</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13905,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Chuyển sang Phrolova.</t>
+          <t>Chuyển sang Phrolova đi</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13970,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Chuyển sang Phrolova.</t>
+          <t>Chuyển sang Phrolova đi</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14035,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đạt tối đa 6.</t>
+          <t>&lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; tối đa là 6.</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14100,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đạt tối đa 6.</t>
+          <t>&lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; tối đa là 6.</t>
         </is>
       </c>
     </row>
@@ -14164,7 +14165,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đạt tối đa 6.</t>
+          <t>&lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; tối đa là 6.</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14230,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Khi nhận được &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới vượt quá giới hạn tối đa, &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt; ngoài cùng bên trái sẽ bị thay thế.</t>
+          <t>Khi nhận được &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới vượt quá giới hạn tối đa, &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Tím&lt;/color&gt; ở ngoài cùng bên trái sẽ bị thay thế.</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14295,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Khi nhận được &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới vượt quá giới hạn tối đa, &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt; ngoài cùng bên trái sẽ bị thay thế.</t>
+          <t>Khi nhận được &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới vượt quá giới hạn tối đa, &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Tím&lt;/color&gt; ở ngoài cùng bên trái sẽ bị thay thế.</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14360,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Khi nhận được &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới vượt quá giới hạn tối đa, &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt; ngoài cùng bên trái sẽ bị thay thế.</t>
+          <t>Khi nhận được &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới vượt quá giới hạn tối đa, &lt;color=Highlight&gt;Forte Gauge - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Tím&lt;/color&gt; ở ngoài cùng bên trái sẽ bị thay thế.</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14425,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Đòn Nặng Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14489,7 +14490,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Đòn Nặng Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14555,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Đòn Nặng Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14620,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Switch Sang Rover</t>
+          <t>Chuyển sang Rover</t>
         </is>
       </c>
     </row>
@@ -14684,7 +14685,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Switch Sang Rover</t>
+          <t>Chuyển sang Rover</t>
         </is>
       </c>
     </row>
@@ -14749,7 +14750,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Switch Sang Rover</t>
+          <t>Chuyển sang Rover</t>
         </is>
       </c>
     </row>
@@ -14814,7 +14815,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Switch về Phrolova.</t>
+          <t>Quay lại với Phrolova đi.</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14880,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Switch về Phrolova.</t>
+          <t>Quay lại với Phrolova đi.</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14945,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Switch về Phrolova.</t>
+          <t>Quay lại với Phrolova đi.</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15010,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Skill của Echo Phrolova</t>
+          <t>Sử dụng Kỹ Năng Vọng Âm của Phrolova.</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15075,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Skill của Echo Phrolova</t>
+          <t>Sử dụng Kỹ Năng Vọng Âm của Phrolova.</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15140,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Skill của Echo Phrolova</t>
+          <t>Sử dụng Kỹ Năng Vọng Âm của Phrolova.</t>
         </is>
       </c>
     </row>
@@ -15204,7 +15205,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Attack để nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;</t>
+          <t>Tấn Công để tích lũy &lt;color=#8c7e51&gt;Năng Lượng Giao Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15269,7 +15270,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Attack để nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;</t>
+          <t>Tấn Công để tích lũy &lt;color=#8c7e51&gt;Năng Lượng Giao Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15335,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Sanhua và Baizhi sẽ tung &lt;color=#8c7e51&gt;Outro Skill để ban buff&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Sanhua và Baizhi sẽ tung &lt;color=#8c7e51&gt;Kỹ Năng Outro để tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15399,7 +15400,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Sanhua và Baizhi sẽ tung &lt;color=#8c7e51&gt;Outro Skill để ban buff&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Sanhua và Baizhi sẽ tung &lt;color=#8c7e51&gt;Kỹ Năng Outro để tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15465,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Sanhua và Baizhi sẽ tung &lt;color=#8c7e51&gt;Outro Skill để ban buff&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Sanhua và Baizhi sẽ tung &lt;color=#8c7e51&gt;Kỹ Năng Outro để tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15530,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Outro Skill của Baizhi cấp buff cho Sanhua</t>
+          <t>Kỹ năng Outro của Baizhi ban thêm hiệu ứng cho Sanhua</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15595,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Outro Skill của Baizhi cấp buff cho Sanhua</t>
+          <t>Kỹ năng Outro của Baizhi ban thêm hiệu ứng cho Sanhua</t>
         </is>
       </c>
     </row>
@@ -15659,7 +15660,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Attack để nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;</t>
+          <t>Tấn Công để tích lũy &lt;color=#8c7e51&gt;Năng Lượng Giao Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15724,7 +15725,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Attack để nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;</t>
+          <t>Tấn Công để tích lũy &lt;color=#8c7e51&gt;Năng Lượng Giao Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15790,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Rover và Sanhua sẽ thi triển &lt;color=#8c7e51&gt;Outro Skill để ban hiệu ứng tăng cường&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Rover và Sanhua sẽ tung &lt;color=#8c7e51&gt;Kỹ Năng Outro để tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15855,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Rover và Sanhua sẽ thi triển &lt;color=#8c7e51&gt;Outro Skill để ban hiệu ứng tăng cường&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Rover và Sanhua sẽ tung &lt;color=#8c7e51&gt;Kỹ Năng Outro để tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15920,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Rover và Sanhua sẽ thi triển &lt;color=#8c7e51&gt;Outro Skill để ban hiệu ứng tăng cường&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Rover và Sanhua sẽ tung &lt;color=#8c7e51&gt;Kỹ Năng Outro để tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15985,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Outro Skill của cả Baizhi và Sanhua đều cấp buff cho Rover</t>
+          <t>Kỹ năng Outro của cả Baizhi và Sanhua đều cấp buff cho Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16050,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Outro Skill của cả Baizhi và Sanhua đều cấp buff cho Rover</t>
+          <t>Kỹ năng Outro của cả Baizhi và Sanhua đều cấp buff cho Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16115,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Concerto Energy đã đầy</t>
+          <t>Năng Lượng Giao Hưởng đã đầy</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16180,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Concerto Energy đã đầy</t>
+          <t>Năng Lượng Giao Hưởng đã đầy</t>
         </is>
       </c>
     </row>
@@ -16244,7 +16245,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Concerto Energy đã đầy</t>
+          <t>Năng Lượng Giao Hưởng đã đầy</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16310,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Concerto Energy đã đầy</t>
+          <t>Năng Lượng Giao Hưởng đã đầy</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16375,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Galbrena tích lũy &lt;color=#8c7e51&gt;Afterflame&lt;/color&gt; và &lt;color=#8c7e51&gt;Sinflame&lt;/color&gt; bằng cách tấn công trong &lt;color=#8c7e51&gt;Threshold State&lt;/color&gt;.</t>
+          <t>Galbrena tích lũy &lt;color=#8c7e51&gt;Dư Lửa&lt;/color&gt; và &lt;color=#8c7e51&gt;Tội Lửa&lt;/color&gt; khi tấn công trong &lt;color=#8c7e51&gt;Trạng Thái Ngưỡng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16440,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Galbrena tích lũy &lt;color=#8c7e51&gt;Afterflame&lt;/color&gt; và &lt;color=#8c7e51&gt;Sinflame&lt;/color&gt; bằng cách tấn công trong &lt;color=#8c7e51&gt;Threshold State&lt;/color&gt;.</t>
+          <t>Galbrena tích lũy &lt;color=#8c7e51&gt;Dư Lửa&lt;/color&gt; và &lt;color=#8c7e51&gt;Tội Lửa&lt;/color&gt; khi tấn công trong &lt;color=#8c7e51&gt;Trạng Thái Ngưỡng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16505,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Galbrena tích lũy &lt;color=#8c7e51&gt;Afterflame&lt;/color&gt; và &lt;color=#8c7e51&gt;Sinflame&lt;/color&gt; bằng cách tấn công trong &lt;color=#8c7e51&gt;Threshold State&lt;/color&gt;.</t>
+          <t>Galbrena tích lũy &lt;color=#8c7e51&gt;Dư Lửa&lt;/color&gt; và &lt;color=#8c7e51&gt;Tội Lửa&lt;/color&gt; khi tấn công trong &lt;color=#8c7e51&gt;Trạng Thái Ngưỡng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16570,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#8c7e51&gt;Sinflame&lt;/color&gt; đầy, sử dụng &lt;color=#8c7e51&gt;Resonance Skill - Ascent of Malice&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=#8c7e51&gt;Demon Hypostasis&lt;/color&gt;. Trong trạng thái &lt;color=#8c7e51&gt;Demon Hypostasis&lt;/color&gt;, các kỹ năng sẽ tiêu hao &lt;color=#8c7e51&gt;Purging Flame&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Khi &lt;color=#8c7e51&gt;Lửa Tội&lt;/color&gt; đạt mức tối đa, sử dụng &lt;color=#8c7e51&gt;Resonance Skill - Thăng Hoa Ác Ý&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=#8c7e51&gt;Hóa Thân Ác Quỷ&lt;/color&gt;. Các kỹ năng sẽ tiêu hao &lt;color=#8c7e51&gt;Lửa Thanh Tẩy&lt;/color&gt; khi trúng mục tiêu trong trạng thái &lt;color=#8c7e51&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16635,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#8c7e51&gt;Sinflame&lt;/color&gt; đầy, sử dụng &lt;color=#8c7e51&gt;Resonance Skill - Ascent of Malice&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=#8c7e51&gt;Demon Hypostasis&lt;/color&gt;. Trong trạng thái &lt;color=#8c7e51&gt;Demon Hypostasis&lt;/color&gt;, các kỹ năng sẽ tiêu hao &lt;color=#8c7e51&gt;Purging Flame&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Khi &lt;color=#8c7e51&gt;Lửa Tội&lt;/color&gt; đạt mức tối đa, sử dụng &lt;color=#8c7e51&gt;Resonance Skill - Thăng Hoa Ác Ý&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=#8c7e51&gt;Hóa Thân Ác Quỷ&lt;/color&gt;. Các kỹ năng sẽ tiêu hao &lt;color=#8c7e51&gt;Lửa Thanh Tẩy&lt;/color&gt; khi trúng mục tiêu trong trạng thái &lt;color=#8c7e51&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16699,7 +16700,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#8c7e51&gt;Sinflame&lt;/color&gt; đầy, sử dụng &lt;color=#8c7e51&gt;Resonance Skill - Ascent of Malice&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=#8c7e51&gt;Demon Hypostasis&lt;/color&gt;. Trong trạng thái &lt;color=#8c7e51&gt;Demon Hypostasis&lt;/color&gt;, các kỹ năng sẽ tiêu hao &lt;color=#8c7e51&gt;Purging Flame&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Khi &lt;color=#8c7e51&gt;Lửa Tội&lt;/color&gt; đạt mức tối đa, sử dụng &lt;color=#8c7e51&gt;Resonance Skill - Thăng Hoa Ác Ý&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=#8c7e51&gt;Hóa Thân Ác Quỷ&lt;/color&gt;. Các kỹ năng sẽ tiêu hao &lt;color=#8c7e51&gt;Lửa Thanh Tẩy&lt;/color&gt; khi trúng mục tiêu trong trạng thái &lt;color=#8c7e51&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16764,7 +16765,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge ngay để kích hoạt Sợi sinh mệnh - Lướt</t>
+          <t>Nhấn Né Tránh ngay bây giờ để thi triển Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16830,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge ngay để kích hoạt Sợi sinh mệnh - Lướt</t>
+          <t>Nhấn Né Tránh ngay bây giờ để thi triển Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
     </row>
@@ -16894,7 +16895,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge ngay để kích hoạt Sợi sinh mệnh - Lướt</t>
+          <t>Nhấn Né Tránh ngay bây giờ để thi triển Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
     </row>
@@ -16959,7 +16960,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge ngay để kích hoạt Sợi sinh mệnh - Lướt</t>
+          <t>Nhấn Né Tránh ngay bây giờ để thi triển Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17025,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge ngay để kích hoạt Sợi sinh mệnh - Lướt</t>
+          <t>Nhấn Né Tránh ngay bây giờ để thi triển Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17090,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge ngay để kích hoạt Sợi sinh mệnh - Lướt</t>
+          <t>Nhấn Né Tránh ngay bây giờ để thi triển Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17155,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Hệ số DMG của Basic Attack và Finisher Attack trong Chainsaw Mode được tăng mạnh</t>
+          <t>Hệ số Sát Thương của Đòn Basic Attack và Đòn Kết Thúc trong Chainsaw Mode được tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17220,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Hệ số DMG của Basic Attack và Finisher Attack trong Chainsaw Mode được tăng mạnh</t>
+          <t>Hệ số Sát Thương của Đòn Basic Attack và Đòn Kết Thúc trong Chainsaw Mode được tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17285,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Hệ số DMG của Basic Attack và Finisher Attack trong Chainsaw Mode được tăng mạnh</t>
+          <t>Hệ số Sát Thương của Đòn Basic Attack và Đòn Kết Thúc trong Chainsaw Mode được tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17350,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đầy, giữ **Basic Attack** để thi triển &lt;color=Highlight&gt;Basic Attack - Spark Collision&lt;/color&gt; và vào trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; đạt tối đa, giữ Đòn Normal Attack để thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Va Chạm Tia Lửa&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17415,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đầy, giữ **Basic Attack** để thi triển &lt;color=Highlight&gt;Basic Attack - Spark Collision&lt;/color&gt; và vào trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; đạt tối đa, giữ Đòn Normal Attack để thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Va Chạm Tia Lửa&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17480,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đầy, giữ **Basic Attack** để thi triển &lt;color=Highlight&gt;Basic Attack - Spark Collision&lt;/color&gt; và vào trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; đạt tối đa, giữ Đòn Normal Attack để thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Va Chạm Tia Lửa&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17544,7 +17545,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Diễu Hành Muôn Sắc&lt;/color&gt;, tấn công và di chuyển sẽ nhận được &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, tấn công và di chuyển sẽ tích lũy &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17610,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Diễu Hành Muôn Sắc&lt;/color&gt;, tấn công và di chuyển sẽ nhận được &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, tấn công và di chuyển sẽ tích lũy &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17675,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Diễu Hành Muôn Sắc&lt;/color&gt;, tấn công và di chuyển sẽ nhận được &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, tấn công và di chuyển sẽ tích lũy &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17739,7 +17740,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt; tiêu hao &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; và phục hồi &lt;color=Highlight&gt;True Color&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack khi &lt;color=Highlight&gt;True Color&lt;/color&gt; đạt tối đa để tung &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack - Nhảy Đa Sắc&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Màu Chân Thật&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack khi &lt;color=Highlight&gt;Màu Chân Thật&lt;/color&gt; đạt tối đa để thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Phún Xạ Sắc Màu&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Basic Attack - Va Chạm Thị Giác&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17804,7 +17805,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt; tiêu hao &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; và phục hồi &lt;color=Highlight&gt;True Color&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack khi &lt;color=Highlight&gt;True Color&lt;/color&gt; đạt tối đa để tung &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack - Nhảy Đa Sắc&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Màu Chân Thật&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack khi &lt;color=Highlight&gt;Màu Chân Thật&lt;/color&gt; đạt tối đa để thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Phún Xạ Sắc Màu&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Basic Attack - Va Chạm Thị Giác&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17869,7 +17870,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt; tiêu hao &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; và phục hồi &lt;color=Highlight&gt;True Color&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack khi &lt;color=Highlight&gt;True Color&lt;/color&gt; đạt tối đa để tung &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack - Nhảy Đa Sắc&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Màu Chân Thật&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack khi &lt;color=Highlight&gt;Màu Chân Thật&lt;/color&gt; đạt tối đa để thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Phún Xạ Sắc Màu&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Basic Attack - Va Chạm Thị Giác&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17935,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ tăng DMG gây ra bởi tất cả Resonators gần đó trong đội.</t>
+          <t>Kích hoạt Resonance Liberation tăng sát thương gây ra bởi tất cả Resonator gần đó trong đội.</t>
         </is>
       </c>
     </row>
@@ -17999,7 +18000,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ tăng DMG gây ra bởi tất cả Resonators gần đó trong đội.</t>
+          <t>Kích hoạt Resonance Liberation tăng sát thương gây ra bởi tất cả Resonator gần đó trong đội.</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18065,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ tăng DMG gây ra bởi tất cả Resonators gần đó trong đội.</t>
+          <t>Kích hoạt Resonance Liberation tăng sát thương gây ra bởi tất cả Resonator gần đó trong đội.</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18130,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Khi đang trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, giữ Resonance Skill để thoát khỏi &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, giữ Resonance Skill để thoát khỏi &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18194,7 +18195,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Khi đang trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, giữ Resonance Skill để thoát khỏi &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, giữ Resonance Skill để thoát khỏi &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18260,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Khi đang trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, giữ Resonance Skill để thoát khỏi &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, giữ Resonance Skill để thoát khỏi &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18325,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để chuyển đổi sang dạng Mech</t>
+          <t>Kích hoạt Resonance Skill để chuyển sang dạng Cơ Giới</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18390,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để chuyển đổi sang dạng Mech</t>
+          <t>Kích hoạt Resonance Skill để chuyển sang dạng Cơ Giới</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18455,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để chuyển đổi sang dạng Mech</t>
+          <t>Kích hoạt Resonance Skill để chuyển sang dạng Cơ Giới</t>
         </is>
       </c>
     </row>
@@ -18519,7 +18520,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để chuyển đổi sang dạng Aemeath</t>
+          <t>Kích hoạt Resonance Skill để chuyển sang dạng Aemeath</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18585,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để chuyển đổi sang dạng Aemeath</t>
+          <t>Kích hoạt Resonance Skill để chuyển sang dạng Aemeath</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18650,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để chuyển đổi sang dạng Aemeath</t>
+          <t>Kích hoạt Resonance Skill để chuyển sang dạng Aemeath</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18715,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Tấn công để tăng Synchronization Rate</t>
+          <t>Tấn công liên tiếp để tăng Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18780,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tấn công để tăng Synchronization Rate</t>
+          <t>Tấn công liên tiếp để tăng Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -18844,7 +18845,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tấn công để tăng Synchronization Rate</t>
+          <t>Tấn công liên tiếp để tăng Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -18909,7 +18910,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Tiêu hao 50% Tỷ lệ Đồng bộ để tung đòn Attack Đồng bộ Nâng cao</t>
+          <t>Tiêu hao 50% Tỷ Lệ Đồng Bộ để kích hoạt Tấn Công Đồng Bộ Nâng Cao.</t>
         </is>
       </c>
     </row>
@@ -18974,7 +18975,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tiêu hao 50% Tỷ lệ Đồng bộ để tung đòn Attack Đồng bộ Nâng cao</t>
+          <t>Tiêu hao 50% Tỷ Lệ Đồng Bộ để kích hoạt Tấn Công Đồng Bộ Nâng Cao.</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19040,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tiêu hao 50% Tỷ lệ Đồng bộ để tung đòn Attack Đồng bộ Nâng cao</t>
+          <t>Tiêu hao 50% Tỷ Lệ Đồng Bộ để kích hoạt Tấn Công Đồng Bộ Nâng Cao.</t>
         </is>
       </c>
     </row>
@@ -19104,7 +19105,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Kích hoạt Enhanced Sync Attack để tăng Resonance Rate</t>
+          <t>Phóng Đòn Đồng Bộ Nâng Cao để tăng Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19170,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Kích hoạt Enhanced Sync Attack để tăng Resonance Rate</t>
+          <t>Phóng Đòn Đồng Bộ Nâng Cao để tăng Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19235,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Kích hoạt Enhanced Sync Attack để tăng Resonance Rate</t>
+          <t>Phóng Đòn Đồng Bộ Nâng Cao để tăng Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19300,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation để tăng Resonance Rate</t>
+          <t>Kích hoạt Resonance Liberation để tăng Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19365,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation để tăng Resonance Rate</t>
+          <t>Kích hoạt Resonance Liberation để tăng Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19429,7 +19430,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation để tăng Resonance Rate</t>
+          <t>Kích hoạt Resonance Liberation để tăng Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19495,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Resonance Liberation có thể sử dụng khi Forte Gauge đầy</t>
+          <t>Resonance Liberation khả dụng khi Thanh Forte đầy.</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19560,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Resonance Liberation có thể sử dụng khi Forte Gauge đầy</t>
+          <t>Resonance Liberation khả dụng khi Thanh Forte đầy.</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19625,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Resonance Liberation có thể sử dụng khi Forte Gauge đầy</t>
+          <t>Resonance Liberation khả dụng khi Thanh Forte đầy.</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19690,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Enter trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Giai đoạn 4&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill Liên hoàn 1&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Vào trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, kỹ năng &lt;color=Highlight&gt;Resonance Skill Liên Kết 1&lt;/color&gt; sẽ được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19755,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Enter trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Giai đoạn 4&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill Liên hoàn 1&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Vào trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, kỹ năng &lt;color=Highlight&gt;Resonance Skill Liên Kết 1&lt;/color&gt; sẽ được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -19819,7 +19820,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Enter trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Giai đoạn 4&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill Liên hoàn 1&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Vào trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, kỹ năng &lt;color=Highlight&gt;Resonance Skill Liên Kết 1&lt;/color&gt; sẽ được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19885,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, nếu Sigrika có ít nhất 50 điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill 2 Liên Kết&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, nếu Sigrika có ít nhất 50 điểm &lt;color=Highlight&gt;Điểm Dừng&lt;/color&gt;, sẽ mở khóa &lt;color=Highlight&gt;Resonance Skill Liên Kết 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19949,7 +19950,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, nếu Sigrika có ít nhất 50 điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill 2 Liên Kết&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, nếu Sigrika có ít nhất 50 điểm &lt;color=Highlight&gt;Điểm Dừng&lt;/color&gt;, sẽ mở khóa &lt;color=Highlight&gt;Resonance Skill Liên Kết 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20015,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, nếu Sigrika có ít nhất 50 điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill 2 Liên Kết&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt;, nếu Sigrika có ít nhất 50 điểm &lt;color=Highlight&gt;Điểm Dừng&lt;/color&gt;, sẽ mở khóa &lt;color=Highlight&gt;Resonance Skill Liên Kết 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20079,7 +20080,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Nếu &lt;color=Highlight&gt;Resonance Skill liên hoàn&lt;/color&gt; trực tiếp trúng mục tiêu trong thời gian di chuyển, Sigrika sẽ nhận được &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt;.</t>
+          <t>Nếu &lt;color=Highlight&gt;Resonance Skill Liên Hoàn&lt;/color&gt; trúng mục tiêu trực tiếp trong thời gian thi triển, Sigrika sẽ nhận được &lt;color=Highlight&gt;Rune: Lời Đáp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20145,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Nếu &lt;color=Highlight&gt;Resonance Skill liên hoàn&lt;/color&gt; trực tiếp trúng mục tiêu trong thời gian di chuyển, Sigrika sẽ nhận được &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt;.</t>
+          <t>Nếu &lt;color=Highlight&gt;Resonance Skill Liên Hoàn&lt;/color&gt; trúng mục tiêu trực tiếp trong thời gian thi triển, Sigrika sẽ nhận được &lt;color=Highlight&gt;Rune: Lời Đáp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20210,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Nếu &lt;color=Highlight&gt;Resonance Skill liên kết&lt;/color&gt; trúng mục tiêu, Sigrika nhận &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt;.</t>
+          <t>Nếu &lt;color=Highlight&gt;Resonance Skill Liên Hoàn&lt;/color&gt; trúng mục tiêu, Sigrika sẽ nhận được &lt;color=Highlight&gt;Rune: Lời Đáp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20275,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Dị Biệt&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; loại đối lập.</t>
+          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Phân Kỳ&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; loại đối lập.</t>
         </is>
       </c>
     </row>
@@ -20339,7 +20340,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Dị Biệt&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; loại đối lập.</t>
+          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Phân Kỳ&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; loại đối lập.</t>
         </is>
       </c>
     </row>
@@ -20404,7 +20405,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Dị Biệt&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; loại đối lập.</t>
+          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Phân Kỳ&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; loại đối lập.</t>
         </is>
       </c>
     </row>
@@ -20469,7 +20470,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Convergent&lt;/color&gt;. Lần tiếp theo nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; cùng loại.</t>
+          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Hội Tụ&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; cùng loại.</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20535,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Convergent&lt;/color&gt;. Lần tiếp theo nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; cùng loại.</t>
+          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Hội Tụ&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; cùng loại.</t>
         </is>
       </c>
     </row>
@@ -20599,7 +20600,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Convergent&lt;/color&gt;. Lần tiếp theo nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; cùng loại.</t>
+          <t>Nếu Sigrika đã có &lt;color=Highlight&gt;Hội Tụ&lt;/color&gt;, lần sau khi nhận được &lt;color=Highlight&gt;Rune&lt;/color&gt; mới, sẽ nhận thêm một &lt;color=Highlight&gt;Rune&lt;/color&gt; cùng loại.</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20665,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao 2 &lt;color=Highlight&gt;Rune&lt;/color&gt; và thực hiện &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt;, đồng thời phục hồi &lt;color=Highlight&gt;Full Stop&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để tiêu hao 2 &lt;color=Highlight&gt;Rune&lt;/color&gt;, tung ra &lt;color=Highlight&gt;Đòn Tấn Công Mạnh Nâng Cao&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20729,7 +20730,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao 2 &lt;color=Highlight&gt;Rune&lt;/color&gt; và thực hiện &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt;, đồng thời phục hồi &lt;color=Highlight&gt;Full Stop&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để tiêu hao 2 &lt;color=Highlight&gt;Rune&lt;/color&gt;, tung ra &lt;color=Highlight&gt;Đòn Tấn Công Mạnh Nâng Cao&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20795,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao 2 &lt;color=Highlight&gt;Rune&lt;/color&gt; và thực hiện &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt;, đồng thời phục hồi &lt;color=Highlight&gt;Full Stop&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để tiêu hao 2 &lt;color=Highlight&gt;Rune&lt;/color&gt;, tung ra &lt;color=Highlight&gt;Đòn Tấn Công Mạnh Nâng Cao&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20860,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Forte Circuit - Learn My True Name.&lt;/color&gt;</t>
+          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20924,7 +20925,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Forte Circuit - Learn My True Name.&lt;/color&gt;</t>
+          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20989,7 +20990,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Forte Circuit - Learn My True Name.&lt;/color&gt;</t>
+          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21054,7 +21055,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Dedication&lt;/color&gt; đạt 300 điểm, &lt;color=Highlight&gt;Frost Splinter - Present Self&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt; đạt 300 điểm, &lt;color=Highlight&gt;Mảnh Băng Giá - Hiện Thân&lt;/color&gt; sẽ sẵn sàng sử dụng.</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21120,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Dedication&lt;/color&gt; đạt 300 điểm, &lt;color=Highlight&gt;Frost Splinter - Present Self&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt; đạt 300 điểm, &lt;color=Highlight&gt;Mảnh Băng Giá - Hiện Thân&lt;/color&gt; sẽ sẵn sàng sử dụng.</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21185,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Dedication&lt;/color&gt; đạt 300 điểm, &lt;color=Highlight&gt;Frost Splinter - Present Self&lt;/color&gt; sẽ khả dụng.</t>
+          <t>Khi &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt; đạt 300 điểm, &lt;color=Highlight&gt;Mảnh Băng Giá - Hiện Thân&lt;/color&gt; sẽ sẵn sàng sử dụng.</t>
         </is>
       </c>
     </row>
@@ -21249,7 +21250,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt 3 tầng, &lt;color=Highlight&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Bitterfrost: Foreclaimed Self&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt 3 stack, &lt;color=Highlight&gt;Đòn Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Bitterfrost: Foreclaimed Self&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21315,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt 3 tầng, &lt;color=Highlight&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Bitterfrost: Foreclaimed Self&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt 3 stack, &lt;color=Highlight&gt;Đòn Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Bitterfrost: Foreclaimed Self&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21379,7 +21380,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt 3 tầng, &lt;color=Highlight&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Bitterfrost: Foreclaimed Self&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt 3 stack, &lt;color=Highlight&gt;Đòn Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Bitterfrost: Foreclaimed Self&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21444,7 +21445,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Di chuyển đến mép vách đá và chuẩn bị lướt</t>
+          <t>Tiến đến mép vách đá và chuẩn bị lướt</t>
         </is>
       </c>
     </row>
@@ -21509,7 +21510,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Dùng Basic Attack hoặc Resonance Skill để nhận 1 tầng "Melody".</t>
+          <t>Dùng đòn Basic Attack hoặc Resonance Skill để nhận 1 tầng "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -21574,7 +21575,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Dùng Basic Attack hoặc Resonance Skill để nhận 1 tầng "Melody".</t>
+          <t>Dùng đòn Basic Attack hoặc Resonance Skill để nhận 1 tầng "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21770,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Gây 1 tầng "Giai Điệu" khi đánh trúng kẻ địch bằng Resonance Skill.</t>
+          <t>Nhận 1 tầng "Giai Điệu" khi trúng đòn Resonance Skill vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -21834,7 +21835,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Gây 1 tầng "Giai Điệu" khi đánh trúng kẻ địch bằng Resonance Skill.</t>
+          <t>Nhận 1 tầng "Giai Điệu" khi trúng đòn Resonance Skill vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -21964,7 +21965,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Heavy Attack không được tăng cường khi không có 3 "Giai Điệu".</t>
+          <t>Đòn Heavy Attack không được tăng cường khi không có 3 "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22030,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Heavy Attack không được tăng cường khi không có 3 "Giai Điệu".</t>
+          <t>Đòn Heavy Attack không được tăng cường khi không có 3 "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22160,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Heavy Attack được tăng cường khi có 3 "Giai Điệu".</t>
+          <t>Đòn Heavy Attack được tăng cường khi bạn có 3 "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -22224,7 +22225,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Heavy Attack được tăng cường khi có 3 "Giai Điệu".</t>
+          <t>Đòn Heavy Attack được tăng cường khi bạn có 3 "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -22354,7 +22355,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Mid-air Attack được tăng cường khi có 3 "Giai điệu".</t>
+          <t>Đòn Mid-air Attack được tăng cường khi có 3 "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -22419,7 +22420,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Mid-air Attack được tăng cường khi có 3 "Giai điệu".</t>
+          <t>Đòn Mid-air Attack được tăng cường khi có 3 "Giai Điệu".</t>
         </is>
       </c>
     </row>
@@ -22486,7 +22487,7 @@
       <c r="M339" t="inlineStr">
         <is>
           <t>Khi có 3 "Giai Điệu" và đang ở trên không
-nhấn {0} để tiêu hao toàn bộ "Giai Điệu" và thực hiện Đòn Lao Xuống được tăng cường.</t>
+{0} để tiêu hao toàn bộ "Giai Điệu" và tung ra một Đòn Lao Xuống được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -22552,8 +22553,8 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Khi có 3 "Giai Điệu" và đang ở giữa không trung
-Dùng Normal Attack để tiêu hao tất cả "Giai Điệu" và thi triển Plunging Attack được tăng cường.</t>
+          <t>Khi có 3 "Giai Điệu" và đang ở trên không
+Dùng Đòn Normal Attack để tiêu hao toàn bộ "Giai Điệu" và tung ra một Đòn Lao Xuống được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -22684,8 +22685,8 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Sau khi tiêu hao 30 Viên Thermobaric Bullets
-nhấn {0} để tung đòn tấn công được tăng cường</t>
+          <t>Sau khi tiêu hao 30 Viên Đạn Nhiệt Áp
+{0} để tung đòn Tấn Công được tăng cường</t>
         </is>
       </c>
     </row>
@@ -22751,8 +22752,8 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Sau khi tiêu hao 30 Viên Thermobaric Bullets
-Chạm để tung đòn Attack được tăng cường</t>
+          <t>Sau khi tiêu hao 30 Viên Đạn Nhiệt Áp
+Nhấn để tung đòn Tấn Công được tăng cường</t>
         </is>
       </c>
     </row>
@@ -22817,7 +22818,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tương tác với ánh sáng vàng để rời domain</t>
+          <t>Tương tác với ánh sáng vàng để rời khỏi khu vực</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22883,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi &lt;color=#8c7e51&gt;thời gian&lt;/color&gt; trên Terminal</t>
+          <t>Cậu có thể điều chỉnh &lt;color=#8c7e51&gt;thời gian&lt;/color&gt; trên Thiết bị đầu cuối của mình.</t>
         </is>
       </c>
     </row>
@@ -23142,7 +23143,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Obsolete</t>
+          <t>Lỗi Thời</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23273,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Chạm để mở Chức Năng.</t>
+          <t>Chạm để mở Chức năng</t>
         </is>
       </c>
     </row>
@@ -23337,7 +23338,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Chạm để sử dụng chức năng.</t>
+          <t>Nhấn Chức Năng.</t>
         </is>
       </c>
     </row>
@@ -23402,7 +23403,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Chạm để mở Map Thu Gọn</t>
+          <t>Chạm để mở Bản đồ nhỏ</t>
         </is>
       </c>
     </row>
@@ -23662,7 +23663,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không.</t>
+          <t>Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không.</t>
         </is>
       </c>
     </row>
@@ -23727,7 +23728,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không.</t>
+          <t>Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không.</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23793,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm để kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không.</t>
+          <t>Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không. Đây là đoạn văn bản thử nghiệm nhằm kiểm tra vấn đề văn bản vượt quá màn hình có được giải quyết hay không.</t>
         </is>
       </c>
     </row>
@@ -23857,7 +23858,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Activity đã mở khóa trong &lt;color=#8c7e51&gt;Sổ Tay Hướng Dẫn&lt;/color&gt;. Nhấn vào đây để mở.</t>
+          <t>Nhiệm vụ Hoạt Động được mở khóa trong &lt;color=#8c7e51&gt;Cẩm Nang Hướng Dẫn&lt;/color&gt;. Nhấn vào đây để mở.</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23923,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Nhấn {0} để sử dụng &lt;color=#8c7e51&gt;Sensor&lt;/color&gt;</t>
+          <t>Nhấn để sử dụng &lt;color=#8c7e51&gt;Cảm Biến&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23987,7 +23988,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Giữ&lt;/color&gt; để mở Menu Công cụ. Di chuột đến &lt;color=#ffd12f&gt;Cảm biến&lt;/color&gt; và thả để chọn</t>
+          <t>Giữ để mở menu Tiện ích. Di chuột qua &lt;color=#ffd12f&gt;Cảm biến&lt;/color&gt; rồi thả ra để chọn.</t>
         </is>
       </c>
     </row>
@@ -24052,7 +24053,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Chạm để dùng &lt;color=#8c7e51&gt;Cảm biến&lt;/color&gt;</t>
+          <t>Chạm để sử dụng &lt;color=#8c7e51&gt;Cảm Biến&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24118,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>{0} Nhấn để sử dụng &lt;color=#8c7e51&gt;Grapple&lt;/color&gt;</t>
+          <t>Nhấn để sử dụng &lt;color=#8c7e51&gt;Móc Câu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24182,7 +24183,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Chạm để dùng &lt;color=#8c7e51&gt;Móc câu&lt;/color&gt;</t>
+          <t>Chạm để sử dụng &lt;color=#8c7e51&gt;Móc Câu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24248,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Chạm để dùng &lt;color=#8c7e51&gt;Echo Skill&lt;/color&gt; này lao về phía trước</t>
+          <t>Chạm để dùng &lt;color=#8c7e51&gt;Kỹ Năng Echo&lt;/color&gt; này lao về phía trước</t>
         </is>
       </c>
     </row>
@@ -24312,7 +24313,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Nhấn và giữ&lt;/color&gt; để mở menu Công cụ. Di chuột đến &lt;color=#8c7e51&gt;Grapple&lt;/color&gt; và thả để chọn</t>
+          <t>Giữ &lt;color=#8c7e51&gt;nhấn&lt;/color&gt; để mở menu Tiện Ích. Di chuột đến &lt;color=#8c7e51&gt;Móc Câu&lt;/color&gt; và thả ra để chọn</t>
         </is>
       </c>
     </row>
@@ -24442,7 +24443,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nhấn {0} để &lt;color=#8c7e51&gt;chuyển&lt;/color&gt; sang thành viên đội có biểu tượng phát sáng để sử dụng &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt; mạnh mẽ</t>
+          <t>Nhấn {0} để &lt;color=#8c7e51&gt;chuyển&lt;/color&gt; sang Cộng Hưởng Giả có biểu tượng phát sáng và sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt; mạnh mẽ</t>
         </is>
       </c>
     </row>
@@ -24507,7 +24508,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang thành viên đội có biểu tượng phát sáng để sử dụng &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt;</t>
+          <t>Chuyển sang thành viên có biểu tượng sáng để sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24572,7 +24573,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Chạm để vào Hướng dẫn Resonator Skill</t>
+          <t>Chạm để vào Hướng Dẫn Kỹ Năng Resonator</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24638,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Chạm Xác nhận để vào</t>
+          <t>Chạm Xác Nhận để vào</t>
         </is>
       </c>
     </row>
@@ -24832,7 +24833,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Mở Danh Mục Resonators để triển khai Resonators</t>
+          <t>Mở Danh Mục Resonator để triển khai Resonator</t>
         </is>
       </c>
     </row>
@@ -24963,7 +24964,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Đội Setup hình
+          <t>Thiết lập Đội
 Chạm vào đây để mở</t>
         </is>
       </c>
@@ -25029,7 +25030,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Mở menu Đội để điều chỉnh đội hình</t>
+          <t>Mở menu Đội Hình để điều chỉnh đội ngũ</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25095,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Chạm để đổi Triệu Tập</t>
+          <t>Chạm để chuyển đổi Hội Tụ</t>
         </is>
       </c>
     </row>
@@ -25159,7 +25160,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>{0} để tăng &lt;color=#8c7e51&gt;Cấp Độ&lt;/color&gt; của Resonator nhằm vượt qua những thử thách sắp tới</t>
+          <t>Nhấn {0} để tăng &lt;color=#8c7e51&gt;Cấp Độ&lt;/color&gt; của Resonator, vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25290,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Auto Chọn để chọn tất cả vật phẩm bạn cần chỉ bằng một lần chạm.</t>
+          <t>Tự Động Chọn để chọn tất cả vật phẩm cần thiết chỉ bằng một chạm.</t>
         </is>
       </c>
     </row>
@@ -25354,7 +25355,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Nhấn &lt;color=#8c7e51&gt;Nhảy&lt;/color&gt; khi đang ở trên không để lướt</t>
+          <t>Chạm &lt;color=#8c7e51&gt;Nhảy&lt;/color&gt; khi đang ở trên không để lướt</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25420,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Chạm để tăng cấp Resonator</t>
+          <t>Chạm để nâng cấp Resonator</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25485,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Increase &lt;color=#8c7e51&gt;Cấp độ&lt;/color&gt; của Resonator để vượt qua thử thách sắp tới</t>
+          <t>Nâng cấp &lt;color=#8c7e51&gt;Cấp độ&lt;/color&gt; của Resonator để vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25550,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Chạm {0} để chuyển đổi Resonators</t>
+          <t>Nhấn {0} để đổi Resonator</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25615,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Chạm tab Resonance Chain</t>
+          <t>Nhấn tab Resonance Chain.</t>
         </is>
       </c>
     </row>
@@ -25679,7 +25680,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -25744,7 +25745,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Echo&lt;/color&gt; đã nhận. Nhấn {0} để xem Echo trong bảng Resonators.</t>
+          <t>&lt;color=#8c7e51&gt;Echo&lt;/color&gt; đã thu thập. Nhấn {0} để xem &lt;color=#8c7e51&gt;Echo&lt;/color&gt; trong bảng Resonator.</t>
         </is>
       </c>
     </row>
@@ -25874,7 +25875,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Mở để xem tất cả Echoes có sẵn</t>
+          <t>Mở để xem tất cả Echo có sẵn</t>
         </is>
       </c>
     </row>
@@ -25939,7 +25940,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Equip để mở khóa Echo Skill và Tăng Chỉ Số</t>
+          <t>Trang bị để mở khóa Kỹ Năng Echo và Tăng Cường Chỉ Số.</t>
         </is>
       </c>
     </row>
@@ -26004,7 +26005,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Echo&lt;/color&gt; đã nhận. View Echo trong bảng Resonators.</t>
+          <t>&lt;color=#8c7e51&gt;Echo&lt;/color&gt; đã thu thập. Xem &lt;color=#8c7e51&gt;Echo&lt;/color&gt; trong bảng Resonator.</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26070,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Chạm vào đây để &lt;color=#8c7e51&gt;chuyển đổi Resonators&lt;/color&gt;</t>
+          <t>Nhấn vào đây để &lt;color=#8c7e51&gt;đổi Resonator&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26199,7 +26200,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Một Resonator mới đã gia nhập nhóm! Nhấn vào biểu tượng &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; để chuyển đổi.</t>
+          <t>Một Resonator mới đã gia nhập đội! Chạm vào biểu tượng &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; để chuyển đổi.</t>
         </is>
       </c>
     </row>
@@ -26264,7 +26265,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Baizhi&lt;/color&gt; đã gia nhập đội. Cô ấy có thể được thêm vào đội hình</t>
+          <t>{0} &lt;color=#8c7e51&gt;Baizhi&lt;/color&gt; đã gia nhập đội. Cô ấy có thể được thêm vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -26329,7 +26330,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Mở menu Đội để điều chỉnh đội hình</t>
+          <t>Mở menu Đội Hình để điều chỉnh đội ngũ</t>
         </is>
       </c>
     </row>
@@ -26394,7 +26395,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Bấm để mở danh sách Resonator và sắp xếp đội hình chiến đấu</t>
+          <t>Nhấn để mở danh sách Resonator và sắp xếp đội hình chiến đấu</t>
         </is>
       </c>
     </row>
@@ -26524,7 +26525,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Baizhi&lt;/color&gt; đã gia nhập đội. Cô ấy có thể được thêm vào đội</t>
+          <t>&lt;color=#8c7e51&gt;Baizhi&lt;/color&gt; đã gia nhập đội. Cô ấy có thể được thêm vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -26589,7 +26590,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>{0} để sử dụng &lt;color=#8c7e51&gt;Grapple&lt;/color&gt;</t>
+          <t>Nhấn {0} để sử dụng &lt;color=#8c7e51&gt;Móc Câu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26654,7 +26655,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Chạm để sử dụng &lt;color=#8c7e51&gt;Grapple&lt;/color&gt;</t>
+          <t>Chạm để sử dụng &lt;color=#8c7e51&gt;Móc Câu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26719,7 +26720,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để nhận &lt;color=#8c7e51&gt;Activity Points&lt;/color&gt;. Quests Activity được làm mới hàng ngày.</t>
+          <t>Hoàn thành nhiệm vụ để nhận &lt;color=#8c7e51&gt;Điểm Hoạt Động&lt;/color&gt;. Các nhiệm vụ Hoạt Động sẽ được làm mới mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -26784,7 +26785,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;EXP Liên Minh&lt;/color&gt; có thể nhận dựa trên Activity Points trong ngày</t>
+          <t>&lt;color=#8c7e51&gt;Kinh nghiệm Liên Minh&lt;/color&gt; có thể nhận dựa trên Điểm Hoạt Động trong ngày</t>
         </is>
       </c>
     </row>
@@ -26849,7 +26850,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Chạm vào Cột mốc để nhận Rewards Giai đoạn</t>
+          <t>Nhấn Cột Mốc để nhận Phần Thưởng Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26915,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để nhận &lt;color=#8c7e51&gt;Activity Points&lt;/color&gt;. Quests Activity được làm mới hàng ngày.</t>
+          <t>Hoàn thành nhiệm vụ để nhận &lt;color=#8c7e51&gt;Điểm Hoạt Động&lt;/color&gt;. Nhiệm vụ Hoạt Động sẽ được làm mới mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -26979,7 +26980,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;EXP Liên Minh&lt;/color&gt; có thể nhận dựa trên Activity Points trong ngày</t>
+          <t>&lt;color=#8c7e51&gt;Kinh nghiệm Liên Minh&lt;/color&gt; có thể nhận dựa trên Điểm Hoạt Động trong ngày</t>
         </is>
       </c>
     </row>
@@ -27044,7 +27045,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chạm vào Cột mốc để nhận Rewards Giai đoạn</t>
+          <t>Nhấn Cột Mốc để nhận Phần Thưởng Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -27109,7 +27110,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Data Bank&lt;/color&gt; đã được mở khóa. Nhấn {0} để đến Terminal xem chi tiết</t>
+          <t>&lt;color=#8c7e51&gt;Ngân hàng Dữ liệu&lt;/color&gt; đã mở khóa. Nhấn {0} để đến &lt;color=#8c7e51&gt;Thiết bị đầu cuối&lt;/color&gt; xem chi tiết.</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27175,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Kiểm tra Cấp độ &lt;color=#8c7e51&gt;Data Bank&lt;/color&gt; và Tiến độ bộ sưu tập &lt;color=#8c7e51&gt;Echo&lt;/color&gt; của bạn</t>
+          <t>Kiểm tra Cấp Độ &lt;color=#8c7e51&gt;Ngân Hàng Dữ Liệu&lt;/color&gt; và Tiến Độ Thu Thập &lt;color=#8c7e51&gt;Echo&lt;/color&gt; của bạn</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27240,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Thu thập thêm Echo để nâng cấp Kho Dữ Liệu của bạn</t>
+          <t>Thu thập thêm Echo để nâng cấp Ngân Hàng Dữ Liệu của cậu</t>
         </is>
       </c>
     </row>
@@ -27369,7 +27370,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Ngân hàng Dữ liệu&lt;/color&gt; đã khả dụng. Đến Terminal để xem chi tiết</t>
+          <t>&lt;color=#8c7e51&gt;Ngân hàng Dữ liệu&lt;/color&gt; đã sẵn sàng. Hãy đến &lt;color=#8c7e51&gt;Thiết bị đầu cuối&lt;/color&gt; để xem chi tiết.</t>
         </is>
       </c>
     </row>
@@ -27434,7 +27435,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chạm để kiểm tra Cấp &lt;color=#8c7e51&gt;Data Bank&lt;/color&gt; và Tiến Độ Bộ Sưu Tập &lt;color=#8c7e51&gt;Echo&lt;/color&gt; của bạn.</t>
+          <t>Chạm để kiểm tra Cấp Độ &lt;color=#8c7e51&gt;Kho Dữ Liệu&lt;/color&gt; và Tiến Độ Thu Thập &lt;color=#8c7e51&gt;Echo&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27499,7 +27500,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Thu thập thêm Echo để nâng cấp Kho Dữ Liệu của bạn</t>
+          <t>Thu thập thêm Echo để nâng cấp Ngân Hàng Dữ Liệu của cậu</t>
         </is>
       </c>
     </row>
@@ -27629,7 +27630,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>{0} để tăng &lt;color=#8c7e51&gt;Cấp Độ Resonator&lt;/color&gt; nhằm vượt qua những thử thách sắp tới</t>
+          <t>Nhấn {0} để tăng &lt;color=#8c7e51&gt;Cấp Độ Resonator&lt;/color&gt;, vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27762,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Level up để nâng cao chỉ số Resonators.</t>
+          <t>Nâng cấp để tăng chỉ số cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -27826,7 +27827,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Increase &lt;color=#8c7e51&gt;Cấp Độ Resonator&lt;/color&gt; để vượt qua những thử thách sắp tới</t>
+          <t>Tăng &lt;color=#8c7e51&gt;Cấp Độ Resonator&lt;/color&gt; để vượt qua thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -27891,7 +27892,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Level up để nâng cao chỉ số Resonators.</t>
+          <t>Nâng cấp để tăng chỉ số cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -27956,7 +27957,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>{0}Increase &lt;color=#8c7e51&gt;Cấp Vũ Khí&lt;/color&gt; để vượt qua thử thách sắp tới</t>
+          <t>Nâng cấp &lt;color=#8c7e51&gt;Cấp Vũ Khí&lt;/color&gt; cho {0} để vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28022,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Thay đổi vũ khí hoặc tăng cấp vũ khí để nâng cao khả năng của Resonator</t>
+          <t>Đổi vũ khí hoặc nâng cấp vũ khí để tăng cường sức mạnh cho Resonator</t>
         </is>
       </c>
     </row>
@@ -28086,7 +28087,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Increase &lt;color=#8c7e51&gt;Weapon Level&lt;/color&gt; để vượt qua những thử thách sắp tới</t>
+          <t>Tăng &lt;color=#8c7e51&gt;Cấp Độ Vũ Khí&lt;/color&gt; để vượt qua thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -28151,7 +28152,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Thay đổi vũ khí hoặc tăng cấp vũ khí để nâng cao khả năng của Resonator</t>
+          <t>Đổi vũ khí hoặc nâng cấp vũ khí để tăng cường sức mạnh cho Resonator</t>
         </is>
       </c>
     </row>
@@ -28216,7 +28217,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>{0} để trang bị và nâng cấp &lt;color=#8c7e51&gt;Echoes&lt;/color&gt; vượt qua thử thách sắp tới</t>
+          <t>Nhấn {0} để trang bị và nâng cấp &lt;color=#8c7e51&gt;Echo&lt;/color&gt;, sẵn sàng vượt qua thử thách phía trước</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28282,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Echoes có thể cung cấp chỉ số bổ sung và hiệu ứng Sonata cho Resonators</t>
+          <t>Echo có thể cung cấp thêm Chỉ Số và Hiệu Ứng Sonata cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -28346,7 +28347,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Equip và nâng cấp &lt;color=#8c7e51&gt;Echoes&lt;/color&gt; để vượt qua những thử thách sắp tới</t>
+          <t>Trang bị và nâng cấp &lt;color=#8c7e51&gt;Echo&lt;/color&gt; để vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28479,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Echoes có thể cung cấp chỉ số bổ sung và hiệu ứng Sonata cho Resonators</t>
+          <t>Echo có thể cung cấp thêm Chỉ Số và Hiệu Ứng Sonata cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28544,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Nâng cấp hoặc Hợp Tấu vũ khí để tăng chỉ số</t>
+          <t>Nâng cấp hoặc Đồng Điệu vũ khí để tăng chỉ số</t>
         </is>
       </c>
     </row>
@@ -28608,7 +28609,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nâng cấp hoặc Hợp Tấu vũ khí để tăng chỉ số</t>
+          <t>Nâng cấp hoặc Đồng Điệu vũ khí để tăng chỉ số</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28674,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Nhấn {0} để mở menu Nhiệm Vụ và xem tất cả Nhiệm Vụ khả dụng</t>
+          <t>Nhấn {0} để mở menu Nhiệm Vụ và xem tất cả nhiệm vụ hiện có</t>
         </is>
       </c>
     </row>
@@ -28738,7 +28739,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Kiểm tra thông tin Nhiệm vụ trong menu Nhiệm vụ</t>
+          <t>Xem thông tin Nhiệm Vụ trong menu Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -28803,7 +28804,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Xem tất cả Nhiệm vụ khả dụng trong menu Nhiệm vụ</t>
+          <t>Xem tất cả Nhiệm Vụ khả dụng trong menu Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -28933,7 +28934,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>{0} to track a Quest</t>
+          <t>Nhấn {0} để theo dõi Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -28998,7 +28999,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Chạm để Theo dõi Nhiệm vụ này</t>
+          <t>Chạm để Theo Dõi Nhiệm Vụ Này</t>
         </is>
       </c>
     </row>
@@ -29063,7 +29064,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Tiêu hao vũ khí giống nhau bằng Syntonize để tăng cường hiệu ứng đặc biệt của chúng</t>
+          <t>Tiêu thụ vũ khí cùng loại để Cảm Ứng và tăng cường hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -29128,7 +29129,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được &lt;color=#8c7e51&gt;Waveband&lt;/color&gt; của Rover. {0} để nâng cao khả năng của Rover.</t>
+          <t>Bạn đã nhận được &lt;color=#8c7e51&gt;Waveband&lt;/color&gt; của Rover. {0} để tăng cường năng lực cho Rover.</t>
         </is>
       </c>
     </row>
@@ -29193,7 +29194,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mở khóa một nút &lt;color=#8c7e51&gt;Resonance Chain&lt;/color&gt; để nâng cao khả năng của Resonator.</t>
+          <t>Mở khóa một nút &lt;color=#8c7e51&gt;Dây Cộng Hưởng&lt;/color&gt; để nâng cao khả năng của Resonator.</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29259,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được &lt;color=#8c7e51&gt;Waveband&lt;/color&gt; của Rover. Nhấn để tăng cường khả năng</t>
+          <t>Bạn đã nhận được &lt;color=#8c7e51&gt;Waveband&lt;/color&gt; của Rover. Nhấn để nâng cấp kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -29323,7 +29324,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Mở khóa một nút &lt;color=#8c7e51&gt;Resonance Chain&lt;/color&gt; để nâng cao khả năng của Resonator.</t>
+          <t>Mở khóa một nút &lt;color=#8c7e51&gt;Dây Cộng Hưởng&lt;/color&gt; để nâng cao khả năng của Resonator.</t>
         </is>
       </c>
     </row>
@@ -29388,7 +29389,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Cẩm Nang&lt;/color&gt; đã mở khóa. Nhấn {0} để xem &lt;color=#8c7e51&gt;Huấn Luyện Combat&lt;/color&gt;</t>
+          <t>&lt;color=#8c7e51&gt;Sổ tay Hướng dẫn&lt;/color&gt; đã mở khóa. Nhấn {0} để xem &lt;color=#8c7e51&gt;Huấn luyện Chiến đấu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29453,7 +29454,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Sổ tay&lt;/color&gt; đã mở khóa. Chạm để xem &lt;color=#8c7e51&gt;Huấn luyện chiến đấu&lt;/color&gt;</t>
+          <t>&lt;color=#8c7e51&gt;Sổ tay Hướng dẫn&lt;/color&gt; đã mở khóa. Chạm để xem &lt;color=#8c7e51&gt;Huấn luyện Chiến đấu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29518,7 +29519,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Khi Hào Quang Điểm Yếu xuất hiện, chạm để kích hoạt &lt;color=#8c7e51&gt;Phản Đòn&lt;/color&gt;</t>
+          <t>Khi Vòng Halo Điểm Yếu xuất hiện, chạm để kích hoạt &lt;color=#8c7e51&gt;Phản Đòn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29583,7 +29584,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Khi Vibration Strength bằng 0, kẻ địch sẽ bị Immobilized. Khi bị Immobilized, kẻ địch không thể thực hiện bất kỳ hành động nào.</t>
+          <t>Khi Độ Rung bằng 0, kẻ địch sẽ bị Cố Định. Khi bị Cố Định, kẻ địch không thể thực hiện bất kỳ hành động nào.</t>
         </is>
       </c>
     </row>
@@ -29648,7 +29649,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Khi Vibration Strength bằng 0, kẻ địch sẽ bị Immobilized. Khi bị Immobilized, kẻ địch không thể thực hiện bất kỳ hành động nào.</t>
+          <t>Khi Độ Rung bằng 0, kẻ địch sẽ bị Cố Định. Khi bị Cố Định, kẻ địch không thể thực hiện bất kỳ hành động nào.</t>
         </is>
       </c>
     </row>
@@ -29778,7 +29779,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Resonators có thể sử dụng &lt;color=#8c7e51&gt;Echo Skill&lt;/color&gt; của Echo được trang bị ở vị trí đầu tiên.</t>
+          <t>Resonator có thể sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Echo&lt;/color&gt; của Echo được trang bị ở vị trí đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -29908,7 +29909,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Resonators có thể sử dụng &lt;color=#8c7e51&gt;Echo Skill&lt;/color&gt; của Echo được trang bị ở vị trí đầu tiên.</t>
+          <t>Resonator có thể sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Echo&lt;/color&gt; của Echo được trang bị ở vị trí đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -29973,7 +29974,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Nhấn {0}/{1} để nhảy qua đoạn đứt đường cao tốc</t>
+          <t>Nhấn {0}/{1} để nhảy qua đoạn đường đứt gãy</t>
         </is>
       </c>
     </row>
@@ -30038,7 +30039,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>{0}Đã đạt giới hạn &lt;color=#8c7e51&gt;Cấp Liên Minh&lt;/color&gt;. Hoàn thành &lt;color=#8c7e51&gt;Nhiệm Vụ Thăng Tiến&lt;/color&gt; để dỡ bỏ giới hạn.</t>
+          <t>{0}Đã đạt đến giới hạn &lt;color=#8c7e51&gt;Cấp Độ Liên Minh&lt;/color&gt;. Hoàn thành &lt;color=#8c7e51&gt;Nhiệm Vụ Thăng Tiến&lt;/color&gt; để dỡ bỏ giới hạn.</t>
         </is>
       </c>
     </row>
@@ -30103,7 +30104,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thăng Cấp &lt;color=#8c7e51&gt;SOL3 Giai đoạn&lt;/color&gt; để gỡ giới hạn &lt;color=#8c7e51&gt;Cấp Liên Minh&lt;/color&gt;.</t>
+          <t>Hoàn thành Nhiệm Vụ Thăng Cấp &lt;color=#8c7e51&gt;GIAI ĐOẠN SOL3&lt;/color&gt; để dỡ bỏ giới hạn &lt;color=#8c7e51&gt;Cấp Độ Liên Minh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30168,7 +30169,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Cấp Liên Minh&lt;/color&gt; đã đạt giới hạn. Hoàn thành &lt;color=#8c7e51&gt;Nhiệm Vụ Thăng Tiến&lt;/color&gt; để dỡ bỏ giới hạn.</t>
+          <t>Đã đạt &lt;color=#8c7e51&gt;Giới hạn Cấp Độ Liên Minh&lt;/color&gt;. Hoàn thành &lt;color=#8c7e51&gt;Nhiệm Vụ Thăng Hoa&lt;/color&gt; để gỡ bỏ giới hạn.</t>
         </is>
       </c>
     </row>
@@ -30233,7 +30234,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thăng Cấp &lt;color=#8c7e51&gt;SOL3 Giai đoạn&lt;/color&gt; để gỡ giới hạn &lt;color=#8c7e51&gt;Cấp Liên Minh&lt;/color&gt;.</t>
+          <t>Hoàn thành Nhiệm Vụ Thăng Cấp &lt;color=#8c7e51&gt;GIAI ĐOẠN SOL3&lt;/color&gt; để dỡ bỏ giới hạn &lt;color=#8c7e51&gt;Cấp Độ Liên Minh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30428,7 +30429,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>{0} Truy cập nhanh các hoạt động khác nhau qua &lt;color=#8c7e51&gt;Sổ Tay Hướng Dẫn&lt;/color&gt;</t>
+          <t>{0} Di chuyển nhanh đến các hoạt động khác nhau qua &lt;color=#8c7e51&gt;Cẩm Nang Hướng Dẫn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30559,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tham gia Weekly Challenge để nhận vật liệu nâng cấp kỹ năng cao cấp</t>
+          <t>Tham gia Thử Thách Hàng Tuần để nhận vật liệu nâng cấp kỹ năng cao cấp.</t>
         </is>
       </c>
     </row>
@@ -30623,7 +30624,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhanh chóng chuyển đến các hoạt động khác nhau qua &lt;color=#8c7e51&gt;Cẩm Nang Hướng Dẫn&lt;/color&gt;</t>
+          <t>Nhanh chóng tham gia các hoạt động khác nhau qua &lt;color=#8c7e51&gt;Sổ Tay Hướng Dẫn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30688,7 +30689,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Nhanh chóng chuyển đến các hoạt động khác nhau qua &lt;color=#8c7e51&gt;Cẩm Nang Hướng Dẫn&lt;/color&gt;</t>
+          <t>Nhanh chóng tham gia các hoạt động khác nhau qua &lt;color=#8c7e51&gt;Sổ Tay Hướng Dẫn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30753,7 +30754,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Tham gia Weekly Challenge để nhận vật liệu nâng cấp kỹ năng cao cấp</t>
+          <t>Tham gia Thử Thách Hàng Tuần để nhận vật liệu nâng cấp kỹ năng cao cấp.</t>
         </is>
       </c>
     </row>
@@ -30818,7 +30819,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Sau khi &lt;color=#8c7e51&gt;Tuning&lt;/color&gt; Echo, các ô Phụ Thuộc tính mới sẽ được thêm vào</t>
+          <t>Sau khi &lt;color=#8c7e51&gt;Điều Chỉnh&lt;/color&gt; một Echo, các ô Phụ Thuộc Tính mới sẽ được bổ sung.</t>
         </is>
       </c>
     </row>
@@ -30883,7 +30884,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Sau khi &lt;color=#8c7e51&gt;Tuning&lt;/color&gt; Echo, các ô Phụ Thuộc tính mới sẽ được thêm vào</t>
+          <t>Sau khi &lt;color=#8c7e51&gt;Điều Chỉnh&lt;/color&gt; một Echo, các ô Phụ Thuộc Tính mới sẽ được bổ sung.</t>
         </is>
       </c>
     </row>
@@ -30948,7 +30949,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Food có thể cung cấp nhiều loại buff cho Resonators</t>
+          <t>Thức ăn có thể mang lại nhiều hiệu ứng tăng cường cho Resonator</t>
         </is>
       </c>
     </row>
@@ -31013,7 +31014,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Nguyên liệu có thể thu thập trên thế giới mở hoặc nhận được từ nấu ăn</t>
+          <t>Nguyên liệu có thể thu thập trên khắp thế giới hoặc chế biến từ nấu ăn.</t>
         </is>
       </c>
     </row>
@@ -31078,7 +31079,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Food có thể cung cấp nhiều loại buff cho Resonators</t>
+          <t>Thức ăn có thể mang lại nhiều hiệu ứng tăng cường cho Resonator</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31144,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nguyên liệu có thể thu thập trên thế giới mở hoặc nhận được từ nấu ăn</t>
+          <t>Nguyên liệu có thể thu thập trên khắp thế giới hoặc chế biến từ nấu ăn.</t>
         </is>
       </c>
     </row>
@@ -31208,7 +31209,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Trong Craft, bạn có thể tạo ra vũ khí mình cần</t>
+          <t>Trong Chế Tạo, bạn có thể chế tạo vũ khí mình cần</t>
         </is>
       </c>
     </row>
@@ -31273,7 +31274,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Weapons được chế tạo từ khuôn, khoáng sản và các vật liệu khác</t>
+          <t>Vũ khí được chế tạo từ khuôn đúc, khoáng sản và các nguyên liệu khác</t>
         </is>
       </c>
     </row>
@@ -31338,7 +31339,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Trong Craft, bạn có thể tạo ra vũ khí mình cần</t>
+          <t>Trong Chế Tạo, bạn có thể chế tạo vũ khí mình cần</t>
         </is>
       </c>
     </row>
@@ -31403,7 +31404,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Weapons được chế tạo từ khuôn, khoáng sản và các vật liệu khác</t>
+          <t>Vũ khí được chế tạo từ khuôn đúc, khoáng sản và các nguyên liệu khác</t>
         </is>
       </c>
     </row>
@@ -31468,7 +31469,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Với Máy Synthesize, bạn có thể tổng hợp Thuốc, chế tạo vật phẩm hoặc tinh luyện vật liệu</t>
+          <t>Với Synthesizer, cậu có thể tổng hợp Thuốc dược, chế tạo vật phẩm hoặc tinh luyện nguyên liệu.</t>
         </is>
       </c>
     </row>
@@ -31533,7 +31534,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Vật liệu có thể thu thập ở thế giới mở hoặc nhận được khi đánh bại kẻ địch cụ thể</t>
+          <t>Vật liệu có thể thu thập trên thế giới mở hoặc nhận được khi đánh bại kẻ địch nhất định.</t>
         </is>
       </c>
     </row>
@@ -31598,7 +31599,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Với Máy Synthesize, bạn có thể tổng hợp Thuốc, chế tạo vật phẩm hoặc tinh luyện vật liệu</t>
+          <t>Với Synthesizer, cậu có thể tổng hợp Thuốc dược, chế tạo vật phẩm hoặc tinh luyện nguyên liệu.</t>
         </is>
       </c>
     </row>
@@ -31663,7 +31664,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Vật liệu có thể thu thập ở thế giới mở hoặc nhận được khi đánh bại kẻ địch cụ thể</t>
+          <t>Vật liệu có thể thu thập trên thế giới mở hoặc nhận được khi đánh bại kẻ địch nhất định.</t>
         </is>
       </c>
     </row>
@@ -31728,7 +31729,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Gây sát thương hoặc Dodge sẽ nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;. Khi đầy, chuyển đổi sang Resonator khác để kích hoạt &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt;.</t>
+          <t>Gây sát thương hoặc né tránh sẽ nhận được &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;. Khi đầy, hãy chuyển đổi sang Resonator khác để kích hoạt &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31793,7 +31794,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Gây sát thương hoặc Dodge sẽ nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;. Khi đầy, chuyển đổi sang Resonator khác để kích hoạt &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt;.</t>
+          <t>Gây sát thương hoặc né tránh sẽ nhận được &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;. Khi đầy, hãy chuyển đổi sang Resonator khác để kích hoạt &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31858,7 +31859,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Chạm để mở bảng Set Thời Gian</t>
+          <t>Chạm để mở bảng Điều chỉnh Thời gian</t>
         </is>
       </c>
     </row>
@@ -31923,7 +31924,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi chuyển sang Rover, bạn sẽ kích hoạt Outro Skill của Chixia và Intro Skill của Rover đồng thời.</t>
+          <t>Khi chuyển sang Rover, bạn sẽ kích hoạt Kỹ Năng Outro của Chixia và Kỹ Năng Intro của Rover đồng thời.</t>
         </is>
       </c>
     </row>
@@ -31988,7 +31989,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khi chuyển sang Rover, bạn sẽ kích hoạt Outro Skill của Chixia và Intro Skill của Rover đồng thời.</t>
+          <t>Khi chuyển sang Rover, bạn sẽ kích hoạt Kỹ Năng Outro của Chixia và Kỹ Năng Intro của Rover đồng thời.</t>
         </is>
       </c>
     </row>
@@ -32053,7 +32054,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Khi chuyển sang Chixia, bạn sẽ kích hoạt Outro Skill của Rover và Intro Skill của Chixia đồng thời.</t>
+          <t>Khi chuyển sang Chixia, bạn sẽ kích hoạt Kỹ Năng Outro của Rover và Kỹ Năng Intro của Chixia đồng thời.</t>
         </is>
       </c>
     </row>
@@ -32118,7 +32119,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Khi chuyển sang Chixia, bạn sẽ kích hoạt Outro Skill của Rover và Intro Skill của Chixia đồng thời.</t>
+          <t>Khi chuyển sang Chixia, bạn sẽ kích hoạt Kỹ Năng Outro của Rover và Kỹ Năng Intro của Chixia đồng thời.</t>
         </is>
       </c>
     </row>
@@ -32183,7 +32184,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể xem Outro Skill tại bảng Resonators</t>
+          <t>{0} Cậu có thể xem Kỹ năng Outro tại bảng Resonator</t>
         </is>
       </c>
     </row>
@@ -32248,7 +32249,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Bạn có thể xem kỹ năng của Resonator tại bảng Skill</t>
+          <t>Bạn có thể xem kỹ năng của Resonator tại bảng Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -32313,7 +32314,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Set giờ</t>
+          <t>Đặt thời gian theo chỉ định</t>
         </is>
       </c>
     </row>
@@ -32378,7 +32379,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Chạm để xem Outro Skill</t>
+          <t>Chạm để xem Kỹ Năng Outro</t>
         </is>
       </c>
     </row>
@@ -32443,7 +32444,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Bạn có thể xem Outro Skill tại bảng Resonator</t>
+          <t>Bạn có thể xem Kỹ Năng Outro tại bảng Resonator</t>
         </is>
       </c>
     </row>
@@ -32508,7 +32509,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Bạn có thể xem kỹ năng của Resonator tại bảng Skill</t>
+          <t>Bạn có thể xem kỹ năng của Resonator tại bảng Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -32638,7 +32639,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>{0} Equip Echoes chỉ định để kích hoạt hiệu ứng &lt;color=#8c7e51&gt;Sonata&lt;/color&gt;</t>
+          <t>{0} Trang bị Echo chỉ định để kích hoạt hiệu ứng &lt;color=#8c7e51&gt;Sonata&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -32703,7 +32704,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Xem Sonata Effect của Echo</t>
+          <t>Kiểm tra Hiệu Ứng Bản Giao Hưởng của Echo</t>
         </is>
       </c>
     </row>
@@ -32833,7 +32834,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Bạn có thể lọc &lt;color=#8c7e51&gt;COST&lt;/color&gt; và bộ &lt;color=#8c7e51&gt;Sonata Effect&lt;/color&gt; của Echo</t>
+          <t>Cậu có thể lọc &lt;color=#8c7e51&gt;CHI PHÍ&lt;/color&gt; và bộ &lt;color=#8c7e51&gt;Hiệu Ứng Sonata&lt;/color&gt; của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32899,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Equip Echoes cùng Sonata để kích hoạt Sonata Effect.</t>
+          <t>Gắn Echo cùng Bản Giao Hưởng để kích hoạt Hiệu Ứng Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -32963,7 +32964,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Equip Echoes cụ thể để kích hoạt hiệu ứng &lt;color=#8c7e51&gt;Sonata&lt;/color&gt;</t>
+          <t>Trang bị Echo cụ thể để kích hoạt hiệu ứng &lt;color=#8c7e51&gt;Sonata&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33028,7 +33029,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi &lt;color=#8c7e51&gt;thời gian&lt;/color&gt; trong Terminal {0}</t>
+          <t>{0} Cậu có thể thay đổi &lt;color=#8c7e51&gt;thời gian&lt;/color&gt; trong Thiết bị đầu cuối của mình</t>
         </is>
       </c>
     </row>
